--- a/public/documents/requirement6/6_1/6_1_modelo_aspetos_ambiental.xlsx
+++ b/public/documents/requirement6/6_1/6_1_modelo_aspetos_ambiental.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\Tec. Qualidade e Sustentabilidade\Sistema de Gestão Ambiental (SGA)\6. Planeamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement6\6_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB280D2-C4C0-40C8-A90F-8BEA115E47E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC23799-1493-4F87-9A81-DD687749FBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Aspetos Ambientais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
-  <si>
-    <t>AVALIAÇÃO DA SIGNIFICÂNCIA DOS ASPETOS AMBIENTAIS</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Aspeto Ambiental (Causa)</t>
   </si>
@@ -59,142 +56,13 @@
     <t>Significância</t>
   </si>
   <si>
-    <t>Deposição em aterro / Esgotamento de solos</t>
-  </si>
-  <si>
-    <t>Significativo</t>
-  </si>
-  <si>
-    <t>Esgotamento de recursos hídricos</t>
-  </si>
-  <si>
-    <t>Moderado</t>
-  </si>
-  <si>
-    <t>Poluição de linhas de água (DGO/DQO)</t>
-  </si>
-  <si>
-    <t>Destruição da camada de ozono / Aquecimento global</t>
-  </si>
-  <si>
-    <t>Poluição sonora (vizinhança de Coimbra)</t>
-  </si>
-  <si>
-    <t>Acumulação de resíduos não biodegradáveis</t>
-  </si>
-  <si>
-    <t>Contaminação química do solo/água</t>
-  </si>
-  <si>
-    <t>Baixo</t>
-  </si>
-  <si>
-    <t>Poluição atmosférica local</t>
-  </si>
-  <si>
-    <t>Contaminação por metais pesados</t>
-  </si>
-  <si>
-    <t>Emissões indiretas de CO2</t>
-  </si>
-  <si>
     <t>Critério de Gravidade</t>
   </si>
   <si>
     <t>Critério de Probabilidade</t>
   </si>
   <si>
-    <t>(Constante): Gerados em todos os turnos de desmancha.</t>
-  </si>
-  <si>
-    <t>(Constante): Uso obrigatório para higiene e refrigeração diária.</t>
-  </si>
-  <si>
-    <t>(Frequente): Lavagem diária das linhas de abate/desmancha.</t>
-  </si>
-  <si>
-    <t>(Improvável): Ocorre apenas em caso de fuga ou manutenção.</t>
-  </si>
-  <si>
-    <t>(Constante): As câmaras de frio nunca desligam (24/7).</t>
-  </si>
-  <si>
-    <t>(Frequente): Funcionamento contínuo das máquinas de frio.</t>
-  </si>
-  <si>
-    <t>(Constante): Todo o produto final é embalado para venda.</t>
-  </si>
-  <si>
-    <t>(Improvável): Manuseamento de detergentes concentrados é controlado.</t>
-  </si>
-  <si>
-    <t>(Frequente): Expedição diária de mercadorias em camiões térmicos.</t>
-  </si>
-  <si>
-    <t>(Improvável): Gerados apenas em manutenção pontual.</t>
-  </si>
-  <si>
-    <t>(Moderado): Impacto significativo no volume de resíduos, mas com destino autorizado.</t>
-  </si>
-  <si>
-    <t>(Menor): Recurso escasso, mas o impacto individual por litro é baixo.</t>
-  </si>
-  <si>
-    <t>(Grave): Elevada carga poluidora (DQO/DBO); risco de multas da APA/ASAE.</t>
-  </si>
-  <si>
-    <t>(Grave): Alto Potencial de Aquecimento Global (GWP) e custo de reposição.</t>
-  </si>
-  <si>
-    <t>(Moderado): Elevada pegada de carbono e custo operacional fixo.</t>
-  </si>
-  <si>
-    <t>(Menor): Impacto limitado à vizinhança imediata em Coimbra.</t>
-  </si>
-  <si>
-    <t>(Menor): Impacto disperso, mas os materiais são recicláveis (Ponto Verde).</t>
-  </si>
-  <si>
-    <t>(Moderado): Pode contaminar a ETAR se for em grande volume.</t>
-  </si>
-  <si>
-    <t>(Moderado): Emissão local de NOₓ e CO₂ em zonas urbanas.</t>
-  </si>
-  <si>
-    <t>(Moderado): Perigosos se misturados com o lixo comum (metais pesados).</t>
-  </si>
-  <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Produção de subprodutos (ossos, gorduras)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Consumo de água (lavagem de carcaças e pavimentos)</t>
-  </si>
-  <si>
-    <t>Rejeição de efluentes com sangue/matéria orgânica</t>
-  </si>
-  <si>
-    <t>Emissões de gases refrigerantes (fugas de F-Gases)</t>
-  </si>
-  <si>
-    <t>Consumo de energia elétrica (câmaras de frio 24h)</t>
-  </si>
-  <si>
-    <t>Ruído das unidades condensadoras e logística</t>
-  </si>
-  <si>
-    <t>Produção de embalagens plásticas e filmes</t>
-  </si>
-  <si>
-    <t>Derrame acidental de produtos de limpeza (detergentes)</t>
-  </si>
-  <si>
-    <t>Emissões de veículos de transporte (gasóleo)</t>
-  </si>
-  <si>
-    <t>Descarte de lâmpadas ou resíduos eletrónicos (E-Waste)</t>
   </si>
 </sst>
 </file>
@@ -245,13 +113,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF814E1D"/>
+        <fgColor rgb="FF203E5E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAA0106"/>
+        <fgColor rgb="FF0F7343"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,6 +224,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -364,9 +235,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,6 +305,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F7343"/>
+      <color rgb="FF203E5E"/>
       <color rgb="FFAA0106"/>
       <color rgb="FF814E1D"/>
       <color rgb="FF420D07"/>
@@ -457,23 +327,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>53786</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>537883</xdr:colOff>
+      <xdr:colOff>80682</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>170180</xdr:rowOff>
+      <xdr:rowOff>98613</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3">
+        <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEF5501-FA1F-53D1-E187-9FAFA36A508D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53ECC2C1-ADEB-39A7-A840-438664F71306}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -495,8 +365,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1844040" cy="1229360"/>
+          <a:off x="125504" y="0"/>
+          <a:ext cx="1192307" cy="1192307"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -830,7 +700,7 @@
   <cols>
     <col min="1" max="1" width="1" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="37.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="32.109375" style="1" bestFit="1" customWidth="1"/>
@@ -841,336 +711,154 @@
     <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="11" t="s">
+    <row r="2" spans="2:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="4" spans="2:10" ht="30" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="4" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>21</v>
+      <c r="H4" s="11" t="s">
+        <v>6</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4">
-        <v>5</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="7">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="5">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
-        <v>5</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7">
-        <v>2</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="5">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="7">
-        <v>4</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="5">
-        <v>16</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="7">
-        <v>4</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="5">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="4">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="7">
-        <v>3</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="5">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="4">
-        <v>4</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="7">
-        <v>2</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="5">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="4">
-        <v>5</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="7">
-        <v>2</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="5">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="4">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="7">
-        <v>3</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="5">
-        <v>6</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="4">
-        <v>4</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="7">
-        <v>3</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="5">
-        <v>12</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="7">
-        <v>3</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="5">
-        <v>6</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/public/documents/requirement6/6_1/6_1_modelo_aspetos_ambiental.xlsx
+++ b/public/documents/requirement6/6_1/6_1_modelo_aspetos_ambiental.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement6\6_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC23799-1493-4F87-9A81-DD687749FBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2805C3AF-F6C8-4669-893E-8B4D4CEE8A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{073A7DA1-8F09-4975-A959-95672E64B932}"/>
   </bookViews>
   <sheets>
     <sheet name="Aspetos Ambientais" sheetId="1" r:id="rId1"/>
+    <sheet name="Avaliação" sheetId="3" r:id="rId2"/>
+    <sheet name="Aspeto - Significado" sheetId="5" r:id="rId3"/>
+    <sheet name="Plano de Ação - Significado" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>Aspeto Ambiental (Causa)</t>
   </si>
@@ -63,13 +66,184 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>PLANO DE AÇÃO</t>
+  </si>
+  <si>
+    <t>ASPETOS AMBIENTAIS</t>
+  </si>
+  <si>
+    <t>MODO DE IMPLEMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>RECURSOS</t>
+  </si>
+  <si>
+    <t>RESPONSÁVEIS</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO E CONFORMIDADES</t>
+  </si>
+  <si>
+    <t>PROBABILIDADE</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Critério</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>Classificação</t>
+  </si>
+  <si>
+    <t>Muito Baixa</t>
+  </si>
+  <si>
+    <t>Insignificante</t>
+  </si>
+  <si>
+    <t>1–5</t>
+  </si>
+  <si>
+    <t>Baixo</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>6–10</t>
+  </si>
+  <si>
+    <t>Moderado</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>11–15</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Elevado</t>
+  </si>
+  <si>
+    <t>16–25</t>
+  </si>
+  <si>
+    <t>Crítico</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
+  </si>
+  <si>
+    <t>CRITÉRIOS DE AVALIAÇÃO</t>
+  </si>
+  <si>
+    <t>COLUNA</t>
+  </si>
+  <si>
+    <t>SIGNIFICADO</t>
+  </si>
+  <si>
+    <t>COMO PREENCHER</t>
+  </si>
+  <si>
+    <t>Descreve como a ação será executada na prática.</t>
+  </si>
+  <si>
+    <t>Indique o método, procedimento, instrução de trabalho, controlo operacional ou etapa do processo. Ex.: "Atualizar procedimento de resíduos", "Criar instrução de armazenamento de químicos".</t>
+  </si>
+  <si>
+    <t>Identifica o que é necessário para realizar a ação.</t>
+  </si>
+  <si>
+    <t>Liste recursos humanos, materiais, equipamentos, orçamento ou tempo necessário. Ex.: "Técnico de Ambiente", "Equipamento de medição", "Consultoria externa".</t>
+  </si>
+  <si>
+    <t>Define quem é responsável por implementar a ação.</t>
+  </si>
+  <si>
+    <t>Indique cargos ou funções responsáveis pela execução. Ex.: "Responsável de Produção", "Gestor de Manutenção".</t>
+  </si>
+  <si>
+    <t>Explica como será verificada a eficácia e conformidade da ação.</t>
+  </si>
+  <si>
+    <t>Indique indicadores, auditorias, medições, verificações ou critérios de conformidade. Ex.: "Auditoria interna", "Checklist de conformidade", "Indicador de redução de resíduos".</t>
+  </si>
+  <si>
+    <t>mostra como será verificada a eficácia e o cumprimento da ação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">define quem implementa; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">indica o que é necessário; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> descreve como a ação será executada; </t>
+  </si>
+  <si>
+    <t>Elemento da atividade, produto ou serviço que interage ou pode interagir com o ambiente.</t>
+  </si>
+  <si>
+    <t>Alteração no ambiente resultante do aspeto ambiental.</t>
+  </si>
+  <si>
+    <t>Grau de ocorrência do impacto ambiental.</t>
+  </si>
+  <si>
+    <t>Descrição do significado do valor atribuído à probabilidade.</t>
+  </si>
+  <si>
+    <t>Intensidade do impacto ambiental caso ocorra.</t>
+  </si>
+  <si>
+    <t>Descrição do significado do valor atribuído à gravidade.</t>
+  </si>
+  <si>
+    <t>Resultado da multiplicação entre probabilidade e gravidade.</t>
+  </si>
+  <si>
+    <t>Classificação final que indica se o aspeto é significativo.</t>
+  </si>
+  <si>
+    <t>Descreva a causa: "Geração de resíduos", "Consumo de água", "Emissão atmosférica", "Ruído", etc.</t>
+  </si>
+  <si>
+    <t>Indique o efeito: "Poluição do solo", "Contaminação da água", "Emissão de GEE", "Perturbação sonora".</t>
+  </si>
+  <si>
+    <t>VERIFICAR AVALIAÇÃO</t>
+  </si>
+  <si>
+    <t>GRAVIDADE</t>
+  </si>
+  <si>
+    <t>SIGNIFICANCIA</t>
+  </si>
+  <si>
+    <t>PLANO DE AÇÃO - Legenda</t>
+  </si>
+  <si>
+    <t>ASPETOS - Legenda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +274,41 @@
       <b/>
       <sz val="24"/>
       <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
     </font>
@@ -201,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,9 +433,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -235,6 +441,52 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -305,8 +557,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF203E5E"/>
       <color rgb="FF0F7343"/>
-      <color rgb="FF203E5E"/>
       <color rgb="FFAA0106"/>
       <color rgb="FF814E1D"/>
       <color rgb="FF420D07"/>
@@ -367,6 +619,171 @@
         <a:xfrm>
           <a:off x="125504" y="0"/>
           <a:ext cx="1192307" cy="1192307"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>617220</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{165851CC-0786-46B4-86FE-3AF415B313D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="83820" y="0"/>
+          <a:ext cx="731520" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B8C3F87-FFFB-4019-8544-997300F9D993}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7620" y="0"/>
+          <a:ext cx="967740" cy="967740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>716280</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68CE3496-753E-4624-8DBD-1195E39A5C81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
+          <a:ext cx="762000" cy="762000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -695,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{665AF76B-7F87-4FDA-9BF1-AE2F3BE94D06}">
-  <dimension ref="B2:J14"/>
+  <dimension ref="B2:O14"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" style="1" customWidth="1"/>
@@ -708,49 +1125,74 @@
     <col min="8" max="8" width="44" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.44140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="2.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="26.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="4" spans="2:10" ht="30" x14ac:dyDescent="0.3">
-      <c r="B4" s="9" t="s">
+    <row r="2" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="L2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+    </row>
+    <row r="4" spans="2:15" ht="30" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -760,8 +1202,12 @@
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
       <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -771,8 +1217,12 @@
       <c r="H6" s="6"/>
       <c r="I6" s="5"/>
       <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -782,8 +1232,12 @@
       <c r="H7" s="6"/>
       <c r="I7" s="5"/>
       <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -793,8 +1247,12 @@
       <c r="H8" s="6"/>
       <c r="I8" s="5"/>
       <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -804,8 +1262,12 @@
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
       <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -815,8 +1277,12 @@
       <c r="H10" s="6"/>
       <c r="I10" s="5"/>
       <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -826,8 +1292,12 @@
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
       <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -837,8 +1307,12 @@
       <c r="H12" s="6"/>
       <c r="I12" s="5"/>
       <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -848,8 +1322,12 @@
       <c r="H13" s="6"/>
       <c r="I13" s="5"/>
       <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -859,10 +1337,15 @@
       <c r="H14" s="6"/>
       <c r="I14" s="5"/>
       <c r="J14" s="3"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:J2"/>
+    <mergeCell ref="L2:O2"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I14">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="between">
@@ -894,4 +1377,452 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1411747-9952-450B-A05F-3935D0CAD10F}">
+  <dimension ref="B2:I10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="14"/>
+      <c r="C2" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="2:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="24"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="17">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="17">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="17">
+        <v>2</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="17">
+        <v>2</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="17">
+        <v>3</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="17">
+        <v>3</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="17">
+        <v>4</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="17">
+        <v>4</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="17">
+        <v>5</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="17">
+        <v>5</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="H4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4616159-A67A-4B7E-BA3B-FDC7CF11103E}">
+  <dimension ref="B2:M7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1" style="20" customWidth="1"/>
+    <col min="2" max="2" width="7" style="20" customWidth="1"/>
+    <col min="3" max="3" width="37.77734375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" style="20" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" style="20" customWidth="1"/>
+    <col min="7" max="7" width="38.88671875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" style="20" customWidth="1"/>
+    <col min="10" max="10" width="29.21875" style="20" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+    </row>
+    <row r="4" spans="2:13" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="str">
+        <f>'Aspetos Ambientais'!B4</f>
+        <v>ID</v>
+      </c>
+      <c r="C4" s="11" t="str">
+        <f>'Aspetos Ambientais'!C4</f>
+        <v>Aspeto Ambiental (Causa)</v>
+      </c>
+      <c r="D4" s="11" t="str">
+        <f>'Aspetos Ambientais'!D4</f>
+        <v>Impacto Ambiental (Efeito)</v>
+      </c>
+      <c r="E4" s="11" t="str">
+        <f>'Aspetos Ambientais'!E4</f>
+        <v>Probabilidade (P)</v>
+      </c>
+      <c r="F4" s="11" t="str">
+        <f>'Aspetos Ambientais'!F4</f>
+        <v>Critério de Probabilidade</v>
+      </c>
+      <c r="G4" s="11" t="str">
+        <f>'Aspetos Ambientais'!G4</f>
+        <v>Gravidade (I)</v>
+      </c>
+      <c r="H4" s="11" t="str">
+        <f>'Aspetos Ambientais'!H4</f>
+        <v>Critério de Gravidade</v>
+      </c>
+      <c r="I4" s="11" t="str">
+        <f>'Aspetos Ambientais'!I4</f>
+        <v>Cálculo (P×I)</v>
+      </c>
+      <c r="J4" s="11" t="str">
+        <f>'Aspetos Ambientais'!J4</f>
+        <v>Significância</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="2:13" s="14" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="2:13" s="14" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91899DE9-38DD-424B-9920-D0567AA8655E}">
+  <dimension ref="B2:E8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="65.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="4" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="str">
+        <f>'Aspetos Ambientais'!L4</f>
+        <v>MODO DE IMPLEMENTAÇÃO</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="str">
+        <f>'Aspetos Ambientais'!M4</f>
+        <v>RECURSOS</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="str">
+        <f>'Aspetos Ambientais'!N4</f>
+        <v>RESPONSÁVEIS</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="str">
+        <f>'Aspetos Ambientais'!O4</f>
+        <v>AVALIAÇÃO E CONFORMIDADES</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>